--- a/Design-Files/Main-Board-V1.1/Deliverables/BOM/JLCPCB_BOM.xlsx
+++ b/Design-Files/Main-Board-V1.1/Deliverables/BOM/JLCPCB_BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\dominikschmidt-meditationdevice\Design-Files\Main-Board-V1.0.0\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\dominikschmidt-meditationdevice\Design-Files\Main-Board-V1.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="244">
   <si>
     <t>Comment</t>
   </si>
@@ -30,21 +30,36 @@
     <t>0.1uF</t>
   </si>
   <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
     <t>22uF</t>
   </si>
   <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
     <t>100nF</t>
   </si>
   <si>
     <t>0.01uF</t>
   </si>
   <si>
+    <t>2.7pF</t>
+  </si>
+  <si>
+    <t>4.7pF</t>
+  </si>
+  <si>
+    <t>18pF</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
     <t>SMF5.0CA</t>
   </si>
   <si>
@@ -57,6 +72,9 @@
     <t>MM3Z3V3B</t>
   </si>
   <si>
+    <t>1N4148W-7-F</t>
+  </si>
+  <si>
     <t>BSMD0805L-200</t>
   </si>
   <si>
@@ -69,15 +87,21 @@
     <t>Voltlink Target</t>
   </si>
   <si>
-    <t>AFC07-S15ECA-00</t>
-  </si>
-  <si>
     <t>DM3BT-DSF-PEJS</t>
   </si>
   <si>
+    <t>FH12-40S-0.5SH(55)</t>
+  </si>
+  <si>
     <t>2.2uH</t>
   </si>
   <si>
+    <t>1.6nH</t>
+  </si>
+  <si>
+    <t>1uH</t>
+  </si>
+  <si>
     <t>XZVG68W-2</t>
   </si>
   <si>
@@ -90,6 +114,9 @@
     <t>AO3400A</t>
   </si>
   <si>
+    <t>BSS123</t>
+  </si>
+  <si>
     <t>5.1K</t>
   </si>
   <si>
@@ -123,18 +150,27 @@
     <t>100K</t>
   </si>
   <si>
-    <t>10R</t>
-  </si>
-  <si>
     <t>100R</t>
   </si>
   <si>
-    <t>470R</t>
-  </si>
-  <si>
     <t>200K</t>
   </si>
   <si>
+    <t>499R</t>
+  </si>
+  <si>
+    <t>562K</t>
+  </si>
+  <si>
+    <t>147K</t>
+  </si>
+  <si>
+    <t>180K</t>
+  </si>
+  <si>
+    <t>95.3K</t>
+  </si>
+  <si>
     <t>TP12422673</t>
   </si>
   <si>
@@ -144,7 +180,7 @@
     <t>EC05E1220401</t>
   </si>
   <si>
-    <t>AMS1117-3.3</t>
+    <t>TPS630250RNCR</t>
   </si>
   <si>
     <t>SLM6600</t>
@@ -162,19 +198,37 @@
     <t>ESP32-WROOM-32E-N8R2</t>
   </si>
   <si>
+    <t>AT42QT1070-MMHR</t>
+  </si>
+  <si>
+    <t>ESP32-S3R8</t>
+  </si>
+  <si>
+    <t>AW9364DNR</t>
+  </si>
+  <si>
+    <t>W25Q128JVSIQ</t>
+  </si>
+  <si>
+    <t>XL9535QF24</t>
+  </si>
+  <si>
+    <t>40MHz</t>
+  </si>
+  <si>
     <t>Designator</t>
   </si>
   <si>
     <t>C1, C11, C12</t>
   </si>
   <si>
-    <t>C2, C4, C7, C13, C14, C15, C18, C24, C25</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>C5</t>
+    <t>C2, C13, C14, C15, C18, C24, C25</t>
+  </si>
+  <si>
+    <t>C3, C5</t>
+  </si>
+  <si>
+    <t>C4</t>
   </si>
   <si>
     <t>C8, C16, C17</t>
@@ -186,18 +240,33 @@
     <t>C10</t>
   </si>
   <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21</t>
+    <t>C19, C33, C41, C44, C49, C50, C51, C53</t>
+  </si>
+  <si>
+    <t>C20, C29, C31, C32, C34, C39, C40, C46, C47, C48, C52</t>
+  </si>
+  <si>
+    <t>C21, C37, C38</t>
   </si>
   <si>
     <t>C22, C23</t>
   </si>
   <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>C42, C43</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
     <t>D1, D2, D3, D4</t>
   </si>
   <si>
@@ -210,6 +279,9 @@
     <t>D12</t>
   </si>
   <si>
+    <t>D13</t>
+  </si>
+  <si>
     <t>F1</t>
   </si>
   <si>
@@ -219,40 +291,49 @@
     <t>J2</t>
   </si>
   <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>J4</t>
+    <t>J3, J4</t>
   </si>
   <si>
     <t>J5</t>
   </si>
   <si>
+    <t>J6</t>
+  </si>
+  <si>
     <t>L1</t>
   </si>
   <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
     <t>LED1</t>
   </si>
   <si>
-    <t>LED2, LED3</t>
+    <t>LED2, LED3, LED4</t>
   </si>
   <si>
     <t>Q1</t>
   </si>
   <si>
-    <t>Q2, Q3, Q4</t>
+    <t>Q2, Q3</t>
+  </si>
+  <si>
+    <t>Q4, Q5, Q6</t>
   </si>
   <si>
     <t>R1, R3</t>
   </si>
   <si>
-    <t>R2, R28, R29, R38</t>
-  </si>
-  <si>
-    <t>R4, R39</t>
-  </si>
-  <si>
-    <t>R5, R15, R26, R30</t>
+    <t>R2, R28, R29, R38, R63, R68</t>
+  </si>
+  <si>
+    <t>R4, R20, R39</t>
+  </si>
+  <si>
+    <t>R5, R15, R26, R30, R33</t>
   </si>
   <si>
     <t>R6</t>
@@ -264,7 +345,7 @@
     <t>R8</t>
   </si>
   <si>
-    <t>R9, R11, R17, R21, R22, R32, R34, R35, R36, R42, R43, R44, R45</t>
+    <t>R9, R11, R17, R21, R22, R32, R35, R36, R42, R43, R44, R45, R50, R51, R52, R53, R60, R61</t>
   </si>
   <si>
     <t>R10</t>
@@ -276,7 +357,7 @@
     <t>R13</t>
   </si>
   <si>
-    <t>R14</t>
+    <t>R14, R34, R47, R48, R49, R54, R56, R57, R58, R59</t>
   </si>
   <si>
     <t>R18</t>
@@ -285,28 +366,37 @@
     <t>R19, R37, R41</t>
   </si>
   <si>
-    <t>R20</t>
-  </si>
-  <si>
     <t>R23, R24</t>
   </si>
   <si>
     <t>R25, R27</t>
   </si>
   <si>
-    <t>R33</t>
-  </si>
-  <si>
     <t>R40</t>
   </si>
   <si>
     <t>R46</t>
   </si>
   <si>
+    <t>R55</t>
+  </si>
+  <si>
+    <t>R64</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>R66</t>
+  </si>
+  <si>
+    <t>R67</t>
+  </si>
+  <si>
     <t>SW1, SW2</t>
   </si>
   <si>
-    <t>SW3</t>
+    <t>SW3, SW5, SW6</t>
   </si>
   <si>
     <t>SW4</t>
@@ -330,6 +420,24 @@
     <t>U6</t>
   </si>
   <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
     <t>Footprint</t>
   </si>
   <si>
@@ -339,15 +447,15 @@
     <t>Cap-0402</t>
   </si>
   <si>
-    <t>Tant-0805</t>
-  </si>
-  <si>
-    <t>Tant-0603</t>
-  </si>
-  <si>
     <t>Cap-0805</t>
   </si>
   <si>
+    <t>Tant-1206</t>
+  </si>
+  <si>
+    <t>CAP-0201</t>
+  </si>
+  <si>
     <t>SOD-123 (Bi-Directional)</t>
   </si>
   <si>
@@ -360,6 +468,9 @@
     <t>SOD323F</t>
   </si>
   <si>
+    <t>SOD-123</t>
+  </si>
+  <si>
     <t>Fuse-0805</t>
   </si>
   <si>
@@ -369,6 +480,12 @@
     <t>YSPI0520-2R2M_</t>
   </si>
   <si>
+    <t>IND-0201</t>
+  </si>
+  <si>
+    <t>PSPMAA0412-1R0M-ANP_</t>
+  </si>
+  <si>
     <t>LED-0402</t>
   </si>
   <si>
@@ -387,10 +504,7 @@
     <t>RES-0805</t>
   </si>
   <si>
-    <t>Res-1206</t>
-  </si>
-  <si>
-    <t>SOT- 223</t>
+    <t>14-VQFN-HR (3x2.5)</t>
   </si>
   <si>
     <t>8-SO-EP_</t>
@@ -408,6 +522,24 @@
     <t>38-SMD Module</t>
   </si>
   <si>
+    <t>20-VQFN (3x3)</t>
+  </si>
+  <si>
+    <t>56-QFN (7x7)</t>
+  </si>
+  <si>
+    <t>DFN-8-EP(2x2)</t>
+  </si>
+  <si>
+    <t>SOIC-8 (208 mil)</t>
+  </si>
+  <si>
+    <t>QFN-24(4x4)</t>
+  </si>
+  <si>
+    <t>X322540MPB4SI_</t>
+  </si>
+  <si>
     <t>LCSC Part Number</t>
   </si>
   <si>
@@ -417,10 +549,10 @@
     <t>C541464</t>
   </si>
   <si>
-    <t>C1954754</t>
-  </si>
-  <si>
-    <t>C1952781</t>
+    <t>C962143</t>
+  </si>
+  <si>
+    <t>C109461</t>
   </si>
   <si>
     <t>C389113</t>
@@ -441,6 +573,21 @@
     <t>C576726</t>
   </si>
   <si>
+    <t>C4984790</t>
+  </si>
+  <si>
+    <t>C325439</t>
+  </si>
+  <si>
+    <t>C505471</t>
+  </si>
+  <si>
+    <t>C106202</t>
+  </si>
+  <si>
+    <t>C326586</t>
+  </si>
+  <si>
     <t>C2980402</t>
   </si>
   <si>
@@ -453,6 +600,9 @@
     <t>C2978865</t>
   </si>
   <si>
+    <t>C83528</t>
+  </si>
+  <si>
     <t>C2757931</t>
   </si>
   <si>
@@ -465,21 +615,30 @@
     <t>C145963</t>
   </si>
   <si>
-    <t>C262588</t>
-  </si>
-  <si>
     <t>C597972</t>
   </si>
   <si>
+    <t>C202114</t>
+  </si>
+  <si>
     <t>C718375</t>
   </si>
   <si>
+    <t>C237384</t>
+  </si>
+  <si>
+    <t>C705331</t>
+  </si>
+  <si>
     <t>C181093</t>
   </si>
   <si>
     <t>C344010</t>
   </si>
   <si>
+    <t>C431506</t>
+  </si>
+  <si>
     <t>C105580</t>
   </si>
   <si>
@@ -519,21 +678,30 @@
     <t>C60491</t>
   </si>
   <si>
-    <t>C108080</t>
-  </si>
-  <si>
     <t>C106235</t>
   </si>
   <si>
     <t>C106232</t>
   </si>
   <si>
-    <t>C114877</t>
-  </si>
-  <si>
     <t>C114763</t>
   </si>
   <si>
+    <t>C137970</t>
+  </si>
+  <si>
+    <t>C273337</t>
+  </si>
+  <si>
+    <t>C163489</t>
+  </si>
+  <si>
+    <t>C852573</t>
+  </si>
+  <si>
+    <t>C276280</t>
+  </si>
+  <si>
     <t>C5381384</t>
   </si>
   <si>
@@ -543,7 +711,7 @@
     <t>C116648</t>
   </si>
   <si>
-    <t>C2992570</t>
+    <t>C2071836</t>
   </si>
   <si>
     <t>C130316</t>
@@ -552,22 +720,37 @@
     <t>C2149796</t>
   </si>
   <si>
+    <t>C361167</t>
+  </si>
+  <si>
     <t>C128370</t>
   </si>
   <si>
     <t>C5361945</t>
   </si>
   <si>
+    <t>C144195</t>
+  </si>
+  <si>
+    <t>C401007</t>
+  </si>
+  <si>
+    <t>C97521</t>
+  </si>
+  <si>
+    <t>C5444301</t>
+  </si>
+  <si>
+    <t>C9010</t>
+  </si>
+  <si>
+    <t>C2913194</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>C2170660</t>
-  </si>
-  <si>
-    <t>C6013564</t>
-  </si>
-  <si>
-    <t>C5374048</t>
-  </si>
-  <si>
-    <t>C2067262</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1027,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,13 +1224,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1055,41 +1238,41 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,13 +1280,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>179</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1111,27 +1294,27 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1139,69 +1322,69 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1209,13 +1392,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,13 +1406,13 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1237,13 +1420,13 @@
         <v>11</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1251,27 +1434,27 @@
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,13 +1462,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1293,13 +1476,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1307,13 +1490,13 @@
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1321,13 +1504,13 @@
         <v>17</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1335,13 +1518,13 @@
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1349,13 +1532,13 @@
         <v>19</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,13 +1546,13 @@
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,13 +1560,13 @@
         <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,13 +1574,13 @@
         <v>22</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,13 +1588,13 @@
         <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,13 +1602,13 @@
         <v>24</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,349 +1616,349 @@
         <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>156</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>157</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>164</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1783,27 +1966,279 @@
         <v>45</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>178</v>
+      <c r="C64" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Design-Files/Main-Board-V1.1/Deliverables/BOM/JLCPCB_BOM.xlsx
+++ b/Design-Files/Main-Board-V1.1/Deliverables/BOM/JLCPCB_BOM.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\dominikschmidt-meditationdevice\Design-Files\Main-Board-V1.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401A667D-033C-44D6-865F-A8CC90741A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="240">
   <si>
     <t>Comment</t>
   </si>
@@ -102,9 +103,6 @@
     <t>1uH</t>
   </si>
   <si>
-    <t>XZVG68W-2</t>
-  </si>
-  <si>
     <t>Red</t>
   </si>
   <si>
@@ -189,12 +187,6 @@
     <t>TPS22919DCKR</t>
   </si>
   <si>
-    <t>TPS3421EGDRYR</t>
-  </si>
-  <si>
-    <t>NC7SZ74K8X</t>
-  </si>
-  <si>
     <t>ESP32-WROOM-32E-N8R2</t>
   </si>
   <si>
@@ -258,9 +250,6 @@
     <t>C35</t>
   </si>
   <si>
-    <t>C36</t>
-  </si>
-  <si>
     <t>C42, C43</t>
   </si>
   <si>
@@ -312,9 +301,6 @@
     <t>LED1</t>
   </si>
   <si>
-    <t>LED2, LED3, LED4</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -330,9 +316,6 @@
     <t>R2, R28, R29, R38, R63, R68</t>
   </si>
   <si>
-    <t>R4, R20, R39</t>
-  </si>
-  <si>
     <t>R5, R15, R26, R30, R33</t>
   </si>
   <si>
@@ -363,9 +346,6 @@
     <t>R18</t>
   </si>
   <si>
-    <t>R19, R37, R41</t>
-  </si>
-  <si>
     <t>R23, R24</t>
   </si>
   <si>
@@ -411,12 +391,6 @@
     <t>U3</t>
   </si>
   <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
     <t>U6</t>
   </si>
   <si>
@@ -513,12 +487,6 @@
     <t>SC-70-6</t>
   </si>
   <si>
-    <t>6-SON (1.45x1)</t>
-  </si>
-  <si>
-    <t>VFSOP-8-2.3mm</t>
-  </si>
-  <si>
     <t>38-SMD Module</t>
   </si>
   <si>
@@ -720,12 +688,6 @@
     <t>C2149796</t>
   </si>
   <si>
-    <t>C361167</t>
-  </si>
-  <si>
-    <t>C128370</t>
-  </si>
-  <si>
     <t>C5361945</t>
   </si>
   <si>
@@ -747,16 +709,43 @@
     <t>C2913194</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>C2170660</t>
+  </si>
+  <si>
+    <t>R4, R69</t>
+  </si>
+  <si>
+    <t>R19, R41</t>
+  </si>
+  <si>
+    <t>C6, C36</t>
+  </si>
+  <si>
+    <t>49.9R</t>
+  </si>
+  <si>
+    <t>R70</t>
+  </si>
+  <si>
+    <t>C114625</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>C2852592</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>C2853065</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1194,9 +1183,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1210,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1224,13 +1213,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,13 +1227,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1252,13 +1241,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1266,13 +1255,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1280,13 +1269,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1294,13 +1283,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1308,13 +1297,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1322,13 +1311,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1336,13 +1325,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1350,13 +1339,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,13 +1353,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1378,13 +1367,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,13 +1381,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1406,13 +1395,13 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1420,13 +1409,13 @@
         <v>11</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,13 +1423,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1448,13 +1437,13 @@
         <v>13</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1462,13 +1451,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,13 +1465,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,13 +1479,13 @@
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,13 +1493,13 @@
         <v>17</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,13 +1507,13 @@
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1532,13 +1521,13 @@
         <v>19</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,13 +1535,13 @@
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,13 +1549,13 @@
         <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,13 +1563,13 @@
         <v>22</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,13 +1591,13 @@
         <v>24</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,13 +1605,13 @@
         <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1630,615 +1619,601 @@
         <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>27</v>
+        <v>238</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B62" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="C68" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Design-Files/Main-Board-V1.1/Deliverables/BOM/JLCPCB_BOM.xlsx
+++ b/Design-Files/Main-Board-V1.1/Deliverables/BOM/JLCPCB_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\dominikschmidt-meditationdevice\Design-Files\Main-Board-V1.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401A667D-033C-44D6-865F-A8CC90741A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9E1DEE-0681-474A-B21F-E99F468300DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,6 @@
     <t>MM3Z3V3B</t>
   </si>
   <si>
-    <t>1N4148W-7-F</t>
-  </si>
-  <si>
     <t>BSMD0805L-200</t>
   </si>
   <si>
@@ -568,9 +565,6 @@
     <t>C2978865</t>
   </si>
   <si>
-    <t>C83528</t>
-  </si>
-  <si>
     <t>C2757931</t>
   </si>
   <si>
@@ -740,6 +734,12 @@
   </si>
   <si>
     <t>C2853065</t>
+  </si>
+  <si>
+    <t>1N5819HW-7-F</t>
+  </si>
+  <si>
+    <t>C82544</t>
   </si>
 </sst>
 </file>
@@ -1199,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1213,13 +1213,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,13 +1227,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1241,13 +1241,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,13 +1255,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1269,13 +1269,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,13 +1283,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1297,13 +1297,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1311,13 +1311,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1325,13 +1325,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,13 +1339,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,13 +1353,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1367,13 +1367,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1381,13 +1381,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,13 +1395,13 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,13 +1409,13 @@
         <v>11</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,13 +1423,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1437,13 +1437,13 @@
         <v>13</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1451,13 +1451,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1465,13 +1465,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,741 +1479,741 @@
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>182</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
